--- a/docs/xlsx/jobs-2026-10-11.xlsx
+++ b/docs/xlsx/jobs-2026-10-11.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="65">
   <si>
     <t>Title</t>
   </si>
@@ -38,13 +38,184 @@
   </si>
   <si>
     <t>Link</t>
+  </si>
+  <si>
+    <t>AI Workflow Lead (London, UK)</t>
+  </si>
+  <si>
+    <t>B Lab</t>
+  </si>
+  <si>
+    <t>London, England, GB</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/02880601cbd748269789a0efec80573b-ai-workflow-lead-london-uk-b-lab-london</t>
+  </si>
+  <si>
+    <t>AI Workflow Lead(Amsterdam, NLD)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/40f1cf016d744513bf348dd0a4a730f7-ai-workflow-leadamsterdam-nld-b-lab-london</t>
+  </si>
+  <si>
+    <t>Communications &amp; PR Manager (Amsterdam, NLD)</t>
+  </si>
+  <si>
+    <t>Amsterdam, North Holland, NL</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/be1920e00c2f46e2a684851e6440f014-communications-pr-manager-amsterdam-nld-b-lab-amsterdam</t>
+  </si>
+  <si>
+    <t>Communications &amp; PR Manager (London, UK)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/dec1ca6e4b6d4bee82f85a17d4105b5e-communications-pr-manager-london-uk-b-lab-london</t>
+  </si>
+  <si>
+    <t>Communications &amp; PR Manager (New York, NY)</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6e465f3bc86b43038cfd1dbc722f0480-communications-pr-manager-new-york-ny-b-lab-new-york</t>
+  </si>
+  <si>
+    <t>Communications &amp; PR Manager (Philadelphia, PA)</t>
+  </si>
+  <si>
+    <t>Philadelphia, Pennsylvania</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9b1753b76ed848e0a0fa01ba5f87777e-communications-pr-manager-philadelphia-pa-b-lab-philadelphia</t>
+  </si>
+  <si>
+    <t>Communications &amp; PR Manager (São Paulo, BR)</t>
+  </si>
+  <si>
+    <t>São Paulo, São Paulo, BR</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1662a34a9825433f94e6d271066df23d-communications-pr-manager-sao-paulo-br-b-lab-sao-paulo</t>
+  </si>
+  <si>
+    <t>Group Leader Arts Education After School</t>
+  </si>
+  <si>
+    <t>Joe's Movement Emporium/World Arts Focus</t>
+  </si>
+  <si>
+    <t>Suitland-Silver Hill, Maryland</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t>USD 18.00 - 20.00/hour</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b885fa235ec9448b8e426d17c09b9a0d-group-leader-arts-education-after-school-joes-movement-emporiumworld-arts-focus-suitland-silver-hill</t>
+  </si>
+  <si>
+    <t>Part-time Accounting Assistant (Contractor)</t>
+  </si>
+  <si>
+    <t>Common Future</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 30.00/hour</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6b68b8a4cf764a3c9e40b2aa21d40424-part-time-accounting-assistant-contractor-common-future-oakland</t>
+  </si>
+  <si>
+    <t>Philanthropy Manager</t>
+  </si>
+  <si>
+    <t>Washington Wildlife and Recreation Coalition</t>
+  </si>
+  <si>
+    <t>Remote (Washington)</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Animals, Environment, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6050f186fd1b479a85c53c5ee8ea74a6-philanthropy-manager-washington-wildlife-and-recreation-coalition-seattle</t>
+  </si>
+  <si>
+    <t>Program Coordinator, Program Manager, Project Coordinator, Project Manager. RATED DC's #1 BEST...</t>
+  </si>
+  <si>
+    <t>Global Language Network</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>USD 43000.00/year</t>
+  </si>
+  <si>
+    <t>Volunteering, Travel Hospitality, International Relations</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fa52d32d791340e5bb54da282403c830-program-coordinator-program-manager-project-coordinator-project-manager-rated-dcs-1-best-global-language-network-washington</t>
+  </si>
+  <si>
+    <t>SACRED Organizing Fellowship (Paid, Part-time, Contract)</t>
+  </si>
+  <si>
+    <t>SACRED</t>
+  </si>
+  <si>
+    <t>Chicago, Illinois</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Civic Engagement, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f286b62729b644e1b6ba94a8380f1723-sacred-organizing-fellowship-paid-part-time-contract-sacred-chicago</t>
+  </si>
+  <si>
+    <t>Senior Events Associate</t>
+  </si>
+  <si>
+    <t>The Honorable Tina Brozman Foundation for Ovarian Cancer Research (Tina's Wish)</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Research Social Science, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/dc38b6a38755463e9c149fb0d607f20c-senior-events-associate-the-honorable-tina-brozman-foundation-for-ovarian-cancer-research-tinas-wish-new-york</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -54,6 +225,10 @@
     </font>
     <font>
       <b/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF1155CC"/>
     </font>
   </fonts>
   <fills count="2">
@@ -76,9 +251,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -514,7 +690,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -553,8 +729,322 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F9" t="s">
+        <v>35</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10" t="s">
+        <v>40</v>
+      </c>
+      <c r="F10" t="s">
+        <v>41</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>46</v>
+      </c>
+      <c r="F11" t="s">
+        <v>47</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
+        <v>52</v>
+      </c>
+      <c r="F12" t="s">
+        <v>53</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>55</v>
+      </c>
+      <c r="B13" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" t="s">
+        <v>57</v>
+      </c>
+      <c r="D13" t="s">
+        <v>33</v>
+      </c>
+      <c r="E13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" t="s">
+        <v>58</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>60</v>
+      </c>
+      <c r="B14" t="s">
+        <v>61</v>
+      </c>
+      <c r="C14" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" t="s">
+        <v>62</v>
+      </c>
+      <c r="F14" t="s">
+        <v>63</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/docs/xlsx/jobs-2026-10-11.xlsx
+++ b/docs/xlsx/jobs-2026-10-11.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="78">
   <si>
     <t>Title</t>
   </si>
@@ -127,6 +127,33 @@
     <t>https://www.idealist.org/en/nonprofit-job/b885fa235ec9448b8e426d17c09b9a0d-group-leader-arts-education-after-school-joes-movement-emporiumworld-arts-focus-suitland-silver-hill</t>
   </si>
   <si>
+    <t>Group Leader, Arts Education After School Program</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b885fa235ec9448b8e426d17c09b9a0d-group-leader-arts-education-after-school-program-joes-movement-emporiumworld-arts-focus-suitland-silver-hill</t>
+  </si>
+  <si>
+    <t>Operations and Development Specialist</t>
+  </si>
+  <si>
+    <t>The Greater Seattle Bureau of Fearless Ideas</t>
+  </si>
+  <si>
+    <t>Remote (Washington)</t>
+  </si>
+  <si>
+    <t>Part Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 30.00 - 30.00/hour</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5f82991944e947a2a7fac6ca5af1055d-operations-and-development-specialist-the-greater-seattle-bureau-of-fearless-ideas-seattle</t>
+  </si>
+  <si>
     <t>Part-time Accounting Assistant (Contractor)</t>
   </si>
   <si>
@@ -151,9 +178,6 @@
     <t>Washington Wildlife and Recreation Coalition</t>
   </si>
   <si>
-    <t>Remote (Washington)</t>
-  </si>
-  <si>
     <t>USD 70000.00 - 85000.00/year</t>
   </si>
   <si>
@@ -209,6 +233,21 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/dc38b6a38755463e9c149fb0d607f20c-senior-events-associate-the-honorable-tina-brozman-foundation-for-ovarian-cancer-research-tinas-wish-new-york</t>
+  </si>
+  <si>
+    <t>Strategic Initiatives Support Officer</t>
+  </si>
+  <si>
+    <t>CIVICUS</t>
+  </si>
+  <si>
+    <t>Full Time, Temporary</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/db52cf914659475ea8575af2048c5ced-strategic-initiatives-support-officer-civicus-johannesburg</t>
   </si>
 </sst>
 </file>
@@ -690,7 +729,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -918,114 +957,183 @@
         <v>37</v>
       </c>
       <c r="B10" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="D10" t="s">
         <v>33</v>
       </c>
       <c r="E10" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="F10" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" t="s">
+        <v>42</v>
+      </c>
+      <c r="E11" t="s">
         <v>43</v>
       </c>
-      <c r="B11" t="s">
+      <c r="F11" t="s">
         <v>44</v>
       </c>
-      <c r="C11" t="s">
+      <c r="H11" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="D11" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" t="s">
-        <v>46</v>
-      </c>
-      <c r="F11" t="s">
-        <v>47</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" t="s">
+        <v>33</v>
+      </c>
+      <c r="E12" t="s">
         <v>49</v>
       </c>
-      <c r="B12" t="s">
+      <c r="F12" t="s">
         <v>50</v>
       </c>
-      <c r="C12" t="s">
+      <c r="H12" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="D12" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" t="s">
-        <v>52</v>
-      </c>
-      <c r="F12" t="s">
-        <v>53</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>52</v>
+      </c>
+      <c r="B13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" t="s">
+        <v>54</v>
+      </c>
+      <c r="F13" t="s">
         <v>55</v>
       </c>
-      <c r="B13" t="s">
+      <c r="H13" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="C13" t="s">
-        <v>57</v>
-      </c>
-      <c r="D13" t="s">
-        <v>33</v>
-      </c>
-      <c r="E13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F13" t="s">
-        <v>58</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B14" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C14" t="s">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="D14" t="s">
         <v>11</v>
       </c>
       <c r="E14" t="s">
+        <v>60</v>
+      </c>
+      <c r="F14" t="s">
+        <v>61</v>
+      </c>
+      <c r="H14" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="F14" t="s">
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>63</v>
       </c>
-      <c r="H14" s="2" t="s">
+      <c r="B15" t="s">
         <v>64</v>
+      </c>
+      <c r="C15" t="s">
+        <v>65</v>
+      </c>
+      <c r="D15" t="s">
+        <v>33</v>
+      </c>
+      <c r="E15" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" t="s">
+        <v>66</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>68</v>
+      </c>
+      <c r="B16" t="s">
+        <v>69</v>
+      </c>
+      <c r="C16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" t="s">
+        <v>70</v>
+      </c>
+      <c r="F16" t="s">
+        <v>71</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>73</v>
+      </c>
+      <c r="B17" t="s">
+        <v>74</v>
+      </c>
+      <c r="C17" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" t="s">
+        <v>75</v>
+      </c>
+      <c r="E17" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" t="s">
+        <v>76</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -1044,6 +1152,9 @@
     <hyperlink ref="H12" r:id="rId11"/>
     <hyperlink ref="H13" r:id="rId12"/>
     <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
